--- a/entertainment_forms/046_script_lab_submission--entertainment_forms.xlsx
+++ b/entertainment_forms/046_script_lab_submission--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,43 +515,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>script_lab_submission</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>script_lab_submission</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select the category for your submission</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe your submission</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select the tool used for your submission</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Form ID</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter a unique form ID</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Output File</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Upload your output file</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>file_description</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>File Description</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Description of the uploaded file</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Duplicate Form ID</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Another unique ID</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,90 +704,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Another Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select another tool</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,10 +739,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -864,6 +827,40 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>chatjimmy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>chatjimmy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
